--- a/DateBase/orders/Dang Nguyen 195_2026-10-1.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-10-1.xlsx
@@ -787,6 +787,9 @@
       <c r="G2" t="str">
         <v>02010105551010510101055555202020201010105101010201010101515</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
